--- a/important_mails_2026-05-10.xlsx
+++ b/important_mails_2026-05-10.xlsx
@@ -1345,7 +1345,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1360,71 +1360,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sun, 3 May 2026 13:18:47 +0000</t>
+          <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 16:23:48 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1443,39 +1393,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1487,39 +1437,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1531,39 +1481,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -1575,39 +1525,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1619,39 +1569,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1663,39 +1613,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1707,39 +1657,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1758,39 +1708,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1809,39 +1759,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -1853,39 +1803,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1897,39 +1847,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1941,39 +1891,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1985,39 +1935,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -2029,39 +1979,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2073,39 +2023,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2117,39 +2067,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2161,39 +2111,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2205,39 +2155,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2249,39 +2199,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2293,39 +2243,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2337,39 +2287,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2381,40 +2331,40 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2433,39 +2383,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2477,39 +2427,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2521,39 +2471,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2565,39 +2515,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2609,39 +2559,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2653,39 +2603,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2706,39 +2656,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2753,39 +2703,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2804,39 +2754,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2860,39 +2810,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2915,39 +2865,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2967,39 +2917,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3015,39 +2965,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3067,39 +3017,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3119,39 +3069,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3171,39 +3121,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3220,39 +3170,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3272,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3324,39 +3274,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3373,39 +3323,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3425,39 +3375,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3471,39 +3421,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3523,39 +3473,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3572,39 +3522,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3620,39 +3570,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3672,39 +3622,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3721,39 +3671,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3765,39 +3715,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3820,39 +3770,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3873,6 +3823,56 @@
  Partita IVA n. LU 20260743.
  Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
  SPC-EUAmazon-1301823410754995</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 3 May 2026 13:18:47 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-05-10.xlsx
+++ b/important_mails_2026-05-10.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 8 May 2026 05:42:00 +0000</t>
+          <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,122 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (zl4CmeMn1C)</t>
+          <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 74
+Quantity Successfully Destroyed: 54
+Quantity Cancelled: 20
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-7548142-6185749
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-2216617652080224</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 16:22:50 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
+ 21,81 €
+https://www.amazon.de/gp/product/B0DRCC2H56/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+SWIMLOOP Premium Schwimmgurt Schwimmtrainer mit 2 x 2 Meter elastischen Gummibändern - Zugseil - Schwimmseil für Pool wie Gegenstromanlage zum Einhängen - Bauchgurt mit Schwimmband Widerstandstraining
+ 69,99 €
+https://www.amazon.de/gp/product/B0C7PJVJK3/?ref_=ci_mcx_mr_2p_0_lm
+Schwimmgurt Erwachsene,4m Einstellbare Schwimmgurt Für Pool,Schwimmtrainer Gegenstromanlage Für Pool, Benutzt Für Schwimmingpools Widerstandstraining （Mit Ohrstöpseln und Nasenclip）
+ 9,24 €
+https://www.amazon.de/gp/product/B097SKBN2X/?ref_=ci_mcx_mr_2p_1_lm
+BodyCROSS Premium Schwimmtrainer Outdoor – Schwimmgürtel für Kinder &amp;amp; Erwachsene mit Tube (1–20kg), Pool Zubehör, Pull Buoy, Schwimmbrett
+ -9 % 114,08 € UVP: 125,97 €
+https://www.amazon.de/gp/product/B01GIMZV8O/?ref_=ci_mcx_mr_2p_2_lm
+TUT Schwimmgürtel, 4-10M S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 05:42:00 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (zl4CmeMn1C)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +645,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -586,39 +697,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -638,39 +749,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -691,39 +802,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -743,39 +854,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -795,87 +906,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 3 May 2026 14:32:02 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Balance paid on your Amazon seller account</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
- Thank you for selling on Amazon.
- Amazon Services
- Help us improve your experience on selling on Amazon through this brief survey:
- https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202605031349
- Was this email helpful?
- SPC-USAmazon-1354600536714402</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -892,39 +955,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -944,39 +1007,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -996,39 +1059,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1045,57 +1108,10 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 3 May 2026 15:00:39 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on Your Selling on Amazon payment account</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
- We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
- Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
- To view your payment activity anytime, please log in to your account and refer the Payments Report page.
- Thank you for selling on Amazon.
- Amazon Payments UK Limited
-Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
- Was this e-mail helpful?
- SPC-EUAmaz</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1110,71 +1126,23 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sun, 3 May 2026 14:45:41 +0000</t>
+          <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Twoja płatność jest już w drodze</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-Ten tytuł będzie wyświetlany na urządzeniach mobilnych
- Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
- Próba wypłaty środków
-Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
-Dnia 05/03/26 14:45 CEST zainicjowaliśmy przelew na kwotę PLN
- 223.89 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
- Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
- Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
- Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
-Więcej o raportach płatności w S</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -1185,39 +1153,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1236,39 +1204,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1292,39 +1260,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1342,39 +1310,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1393,39 +1361,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1437,39 +1405,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1481,39 +1449,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -1525,39 +1493,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1569,39 +1537,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1613,39 +1581,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1657,39 +1625,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1708,39 +1676,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1759,39 +1727,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -1803,39 +1771,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1847,39 +1815,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1891,39 +1859,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1935,39 +1903,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -1979,39 +1947,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2023,39 +1991,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2067,39 +2035,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2111,39 +2079,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2155,39 +2123,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2199,39 +2167,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2243,39 +2211,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2287,39 +2255,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2331,40 +2299,40 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2383,39 +2351,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2427,39 +2395,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2471,39 +2439,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2515,39 +2483,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2559,39 +2527,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2603,39 +2571,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2656,39 +2624,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2703,39 +2671,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2754,39 +2722,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2810,39 +2778,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2865,6 +2833,54 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 3 May 2026 14:32:02 +0000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202605031349
+ Was this email helpful?
+ SPC-USAmazon-1354600536714402</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -3035,21 +3051,116 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Sat, 2 May 2026 15:23:38 +0000</t>
+          <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>跨账户负余额调整</t>
+          <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+ We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
+ Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
+ To view your payment activity anytime, please log in to your account and refer the Payments Report page.
+ Thank you for selling on Amazon.
+ Amazon Payments UK Limited
+Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+ Was this e-mail helpful?
+ SPC-EUAmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 3 May 2026 14:45:41 +0000</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Twoja płatność jest już w drodze</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>96
+Ten tytuł będzie wyświetlany na urządzeniach mobilnych
+ Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
+ Próba wypłaty środków
+Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
+Dnia 05/03/26 14:45 CEST zainicjowaliśmy przelew na kwotę PLN
+ 223.89 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
+ Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
+ Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
+ Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
+Więcej o raportach płatności w S</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 2 May 2026 15:23:38 +0000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>跨账户负余额调整</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3069,39 +3180,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3121,39 +3232,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3170,39 +3281,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3222,39 +3333,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3274,39 +3385,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3323,39 +3434,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3375,39 +3486,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3421,39 +3532,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3473,39 +3584,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3522,39 +3633,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3570,39 +3681,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3622,39 +3733,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3671,39 +3782,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3715,39 +3826,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3770,39 +3881,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3826,39 +3937,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3876,39 +3987,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3926,39 +4037,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3976,39 +4087,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4026,39 +4137,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4074,39 +4185,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4124,39 +4235,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4174,39 +4285,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4216,39 +4327,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4269,39 +4380,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4317,39 +4428,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4368,39 +4479,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4411,39 +4522,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4462,39 +4573,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4513,39 +4624,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4564,39 +4675,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4616,39 +4727,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4677,39 +4788,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4727,39 +4838,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4777,39 +4888,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4827,39 +4938,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4873,39 +4984,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4923,40 +5034,40 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4973,40 +5084,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5023,39 +5134,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -5089,39 +5200,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -5136,39 +5247,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -5184,39 +5295,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -5240,39 +5351,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5291,39 +5402,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -5339,39 +5450,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -5383,39 +5494,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5435,39 +5546,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5485,90 +5596,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0FCDRNTT8" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-Once you have corrected the problems listed above, please re-upload a valid document in "Manage Your Compliance" on "Provide documents" section.
-For any questions/appeals regarding this product/other products, please submit them ( for each ASIN separately ) in "Manage Your Compliance" on the relevant Appeal reason:
-1. Go to the Performance tab and select Account health.
-2. Under Manage your compliance in the bottom right corner, click Product compliance requests.
-3. Click Add or appeal compliance button for the product you’re taking action on.
-4. To upload the documentation, drag and drop fil</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5590,39 +5650,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -5648,40 +5708,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5697,40 +5757,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5746,39 +5806,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5794,39 +5854,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5842,39 +5902,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5890,39 +5950,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5936,39 +5996,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5986,40 +6046,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6035,39 +6095,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6083,39 +6143,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6131,40 +6191,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6180,39 +6240,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6229,39 +6289,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6290,39 +6350,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6338,39 +6398,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6384,39 +6444,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6431,39 +6491,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6483,39 +6543,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -6544,40 +6604,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -6590,39 +6650,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -6637,39 +6697,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -6682,40 +6742,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -6730,40 +6790,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -6777,39 +6837,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -6823,39 +6883,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -6870,39 +6930,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -6916,39 +6976,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -6963,39 +7023,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7010,39 +7070,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7061,39 +7121,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7109,39 +7169,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7162,39 +7222,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7212,40 +7272,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7263,39 +7323,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7312,39 +7372,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7362,40 +7422,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7413,39 +7473,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7463,39 +7523,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7512,39 +7572,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7559,39 +7619,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7610,39 +7670,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -7660,39 +7720,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -7731,39 +7791,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7779,40 +7839,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7828,39 +7888,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7876,39 +7936,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7922,40 +7982,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7971,39 +8031,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8019,39 +8079,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8072,39 +8132,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8119,39 +8179,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8168,39 +8228,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8214,39 +8274,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -8265,40 +8325,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -8312,61 +8372,10 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
- Reglamento relativo a la seguridad general de los productos</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>96
- Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
- Hola, Weihai EU:
- Algunos de los listings de nuestras tiendas de la UE se han desactivado debido a que falta información de cumplimiento normativo obligatoria. Esta medida no afecta al estado de tu cuenta.
- Encontrarás ejemplos de listings desactivados al final de este correo electrónico y la lista completa en la página "Estado de la cuenta". Revisa los listings afectados y siguientes pasos para cumplir los requisitos del Reglamento relativo a la seguridad general de los productos que se indican a continuación.
- Presentar información sobre cumplimiento normativo
- Presentar información sobre cumplimiento normativo
- ¿Cómo puedo reactivar mis listings?
- Para reactivar tus listings, proporciona la información obligatoria del Reglamento relativo a la seguridad general de los productos. Para ello, sigue las instrucciones que se indican a continuación:
--
- Ve a la página "Estado de la cuenta" .
-- Selecciona "Añadir filtros" y marca "Listing retirado" en la columna "Filtrar según las medidas tomadas".
-- Haz clic en "Enviar" junto al listing desactivado y sigue las</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8381,184 +8390,21 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
+          <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Hello from Berlin,
-Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
-quality award for your product "Roaxkois Schwimmgurt für Pool".
-Please let me know whether:
-  * this could be relevant for you, or
-  * I should follow up at a later time
-Best regards,
-Justin
-\--
-**Justin Bangina**
-Junior Sales Manager B2B
-[Hier einen Termin buchen, um mehr über Vergleich.org zu
-erfahren!](https://calendly.com/justin-bangina/vgl-vorstellung)
-E-Mail: [justin.bangina@vergleich.org](mailto:justin.bangina@vergleich.org)
-Telefon: +49 30 83 79 07 04
-![](https://closeio-
-filepicker.s3.amazonaws.com/2024-06-20%2F7fFa6RzdGpCb8T72iZD05S%2F1718867565153-image.png)
-![](https://closeio-
-filepicker.s3.amazonaws.com/03Vs0h0DapPjar7ToXtW0a%2F1626342130359-1626342130359.png)
-[**Vergleich.org**](http://vergleich.org/)**  | VGL Publishing AG**
-Internet: [https://www.vergleich.org](https://www.vergleich.org/)
-Oranienstraße 6, 10997 Berlin
-Vorstand: Jan Steffen &amp; Timo Schürmann,
-Aufsichtsratsvorsitzender: Michael Riedl
-Amtsgericht Berlin (Charlottenburg), HRB 243307 B
-USt-Identifikationsnummer: DE296826903
-![image.png](https://closeio-
-filepicker.s3.amazonaws.com/2026-01-15%2F0U3zStfuGla1fho9cU</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>Introducing Global Warehousing &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>96
- Store inventory at origin in China with lower costs and faster speeds.
- Hello,
- Starting April 9, 2026, you can store your inventory in bulk at a lower cost in our new Global Warehousing &amp; Distribution (GWD) facility in Shenzhen, China, and seamlessly replenish to our US fulfillment network when needed.
- By using GWD in Shenzhen, you can:
-- Reduce storage costs by up to 45% compared to US Amazon Warehousing and Distribution (AWD).
-- Get inventory to US fulfillment centers up to seven days faster when paired with Amazon Global Logistics (AGL).
-- Maintain consistently healthy inventory levels through reliable, automated cross-border replenishment.
-- Choose your management style of either AI-powered automated replenishment or manual control while we handle the entire cross-border logistics process.
-- Streamline your supply chain of shipping, customs clearance, and delivery to our fulfillment centers all through a single, integrated solution. GWD is the first step in our Next Generation of Global Selling vision — where you list once, bring your inventory to the warehouse at origin, and sell it globally from day one. This vision transforms cross-border commerce: you focus on buildin</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ca
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 04:46:00 +0000</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8582,39 +8428,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8638,39 +8484,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8691,39 +8537,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8745,39 +8591,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8800,39 +8646,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8853,39 +8699,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8908,39 +8754,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -8970,39 +8816,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9051,39 +8897,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9092,39 +8938,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -9140,54 +8986,6 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-C2S2 PCP Pallet Limited Time Promotion
-Dear Selling Partner,
-Ready to unlock European growth? Join Customs Clearance and Shipping Service (C2S2) PCP Pallets and get an unbeatable launch package: up to €240 in transportation fee reimbursements per shipment during our Spring Promotion (April 10 - June 30, 2026), PLUS 1 year of free Indirect Representation (IR) worth €200, PLUS your first shipment worth €60 completely free.
-It's the perfect time to start shipping cross-border with confidence. Join for free to the PCP-AVASK Pallet solution today.
-[Enroll now with AVASK](https://go.amazonsellerservices.com/e/229492/jfe-form-SV-cA1EXJ0WHz20OFg/7z2qvf2/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-- Automatic tracking: No claims process - we track your shipments automatically
-- Check full [terms and conditions here](https://go.amazonsellerservices.com/e/229492/-C2S2-LTL-Q2-Promotion-TCs-pdf/7z2qvf5/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-Offer Details:
-Pallets per Shipment                               Your Savings
-1-5 pallets    </t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
